--- a/slides/tt1/checking_points.xlsx
+++ b/slides/tt1/checking_points.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\suine\project\mindvault\slides\tt1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{45977A13-F144-4754-89BE-B3C63A448F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9360" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务列表" sheetId="1" r:id="rId1"/>
@@ -12,6 +18,7 @@
     <sheet name="WpsReserved_CellImgList" sheetId="2" state="veryHidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -440,46 +447,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="36">
-    <numFmt numFmtId="176" formatCode="\¥#,##0.00;[Red]\¥\-#,##0.00"/>
-    <numFmt numFmtId="177" formatCode="#\ ??/??"/>
-    <numFmt numFmtId="24" formatCode="\$#,##0_);[Red]\(\$#,##0\)"/>
-    <numFmt numFmtId="7" formatCode="&quot;￥&quot;#,##0.00;&quot;￥&quot;\-#,##0.00"/>
-    <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
-    <numFmt numFmtId="23" formatCode="\$#,##0_);\(\$#,##0\)"/>
-    <numFmt numFmtId="25" formatCode="\$#,##0.00_);\(\$#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="[$-804]aaaa"/>
-    <numFmt numFmtId="179" formatCode="h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="8" formatCode="&quot;￥&quot;#,##0.00;[Red]&quot;￥&quot;\-#,##0.00"/>
-    <numFmt numFmtId="180" formatCode="mmmmm"/>
-    <numFmt numFmtId="181" formatCode="[DBNum1]上午/下午h&quot;时&quot;mm&quot;分&quot;"/>
-    <numFmt numFmtId="182" formatCode="[DBNum1][$-804]m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="5" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="183" formatCode="mmmmm\-yy"/>
-    <numFmt numFmtId="184" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="185" formatCode="#\ ?/?"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="186" formatCode="[DBNum1]h&quot;时&quot;mm&quot;分&quot;"/>
-    <numFmt numFmtId="187" formatCode="mmmm\-yy"/>
-    <numFmt numFmtId="188" formatCode="[DBNum1][$-804]yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="189" formatCode="yy/m/d"/>
-    <numFmt numFmtId="190" formatCode="\¥#,##0;\¥\-#,##0"/>
-    <numFmt numFmtId="191" formatCode="\¥#,##0.00;\¥\-#,##0.00"/>
-    <numFmt numFmtId="192" formatCode="#\ ??"/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="193" formatCode="[$-804]aaa"/>
-    <numFmt numFmtId="194" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="6" formatCode="&quot;￥&quot;#,##0;[Red]&quot;￥&quot;\-#,##0"/>
-    <numFmt numFmtId="195" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
-    <numFmt numFmtId="196" formatCode="yyyy/m/d\ h:mm\ AM/PM"/>
-    <numFmt numFmtId="197" formatCode="h:mm\ AM/PM"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="198" formatCode="m/d"/>
-    <numFmt numFmtId="199" formatCode="[DBNum1][$-804]yyyy&quot;年&quot;m&quot;月&quot;"/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -514,151 +483,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,194 +520,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -902,251 +547,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1154,126 +557,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1287,6 +646,19 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>57785</xdr:rowOff>
     </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name=" 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr/>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1544,392 +916,394 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="12.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
-    <col min="2" max="2" width="47.6" customWidth="1"/>
+    <col min="2" max="2" width="47.625" customWidth="1"/>
     <col min="3" max="3" width="45.625" customWidth="1"/>
     <col min="4" max="4" width="56.875" customWidth="1"/>
-    <col min="5" max="5" width="38.45" customWidth="1"/>
+    <col min="5" max="5" width="38.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.75" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" ht="15.75" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.15">
+      <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:5">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5">
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.15">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="2">
         <v>950</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" ht="17.25" spans="1:5">
-      <c r="A5" s="7" t="s">
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="1:5">
-      <c r="A6" s="7"/>
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A6" s="17"/>
+      <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="1:5">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" ht="33" spans="1:5">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8" t="s">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.15">
+      <c r="A8" s="17"/>
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="50.25" spans="1:5">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:5" ht="49.5" x14ac:dyDescent="0.15">
+      <c r="A9" s="17"/>
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" ht="17.25" spans="1:5">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8" t="s">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="17"/>
+      <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" ht="33.75" spans="1:5">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8" t="s">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.15">
+      <c r="A11" s="17"/>
+      <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" ht="50.25" spans="1:5">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8" t="s">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="49.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="17"/>
+      <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" ht="17.25" spans="1:5">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8" t="s">
+    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A13" s="17"/>
+      <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" ht="17.25" spans="1:5">
-      <c r="A14" s="7"/>
-      <c r="B14" s="10" t="s">
+    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A14" s="17"/>
+      <c r="B14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" ht="33.75" spans="1:5">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:5" ht="33" x14ac:dyDescent="0.15">
+      <c r="A15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="33.75" spans="1:5">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8" t="s">
+    <row r="16" spans="1:5" ht="33" x14ac:dyDescent="0.15">
+      <c r="A16" s="17"/>
+      <c r="B16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" ht="17.25" spans="1:5">
-      <c r="A17" s="7"/>
-      <c r="B17" s="10" t="s">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A17" s="17"/>
+      <c r="B17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="19"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="14" t="s">
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A18" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="14"/>
-      <c r="B19" s="8" t="s">
+    <row r="19" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A19" s="18"/>
+      <c r="B19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" ht="17.25" spans="1:5">
-      <c r="A20" s="14"/>
-      <c r="B20" s="8" t="s">
+    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A20" s="18"/>
+      <c r="B20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A21" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="14" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A22" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="14"/>
-      <c r="B23" s="17" t="s">
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="18"/>
+      <c r="B23" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="17" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B24" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="11" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
   <mergeCells count="10">
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<autofilters xmlns="https://web.wps.cn/et/2018/main"/>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="3"/>
+  <pixelatorList sheetStid="2"/>
+</pixelators>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1951,15 +1325,11 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="3"/>
-  <pixelatorList sheetStid="2"/>
-</pixelators>
+<autofilters xmlns="https://web.wps.cn/et/2018/main"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5662047-3127-477A-AC3A-1D340467FB41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -1977,7 +1347,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5662047-3127-477A-AC3A-1D340467FB41}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>

--- a/slides/tt1/checking_points.xlsx
+++ b/slides/tt1/checking_points.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\suine\project\mindvault\slides\tt1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{45977A13-F144-4754-89BE-B3C63A448F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{90CACBD7-0B83-4420-A457-3A83B8442119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务列表" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>TODO：</t>
   </si>
@@ -396,9 +396,6 @@
     <t>运行配置</t>
   </si>
   <si>
-    <t>容器操作系统</t>
-  </si>
-  <si>
     <t>openEuler 24.03 (LTS-SP3)</t>
   </si>
   <si>
@@ -408,9 +405,6 @@
     <t>不绑定 NUMA （客户要求）</t>
   </si>
   <si>
-    <t>核数</t>
-  </si>
-  <si>
     <t>384/384(2p)</t>
   </si>
   <si>
@@ -442,13 +436,49 @@
   </si>
   <si>
     <t>install.sh 是否指定了镜像版本</t>
+  </si>
+  <si>
+    <t>测试脚本</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>./bin/cube-bench</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>模板镜像</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>待确认（当前使用的是 sandbox-code:latest)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙箱操作系统</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Host核数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙箱 vCore</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙箱内存</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>24*64G DDR5 6400MT/s</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,6 +517,29 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -553,7 +606,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -584,6 +637,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -613,6 +669,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -929,7 +1000,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
     </row>
@@ -942,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
@@ -953,13 +1024,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
@@ -969,33 +1040,33 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.15">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="17" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.15">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="2">
         <v>950</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="16"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1004,15 +1075,15 @@
       <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="17"/>
+      <c r="A6" s="18"/>
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
@@ -1022,12 +1093,12 @@
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1042,7 +1113,7 @@
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A8" s="17"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -1057,7 +1128,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="49.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="17"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
@@ -1068,7 +1139,7 @@
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="17"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
@@ -1079,7 +1150,7 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A11" s="17"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
@@ -1092,7 +1163,7 @@
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" ht="49.5" x14ac:dyDescent="0.15">
-      <c r="A12" s="17"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
@@ -1107,7 +1178,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A13" s="17"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
@@ -1122,7 +1193,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="6" t="s">
         <v>34</v>
       </c>
@@ -1132,12 +1203,12 @@
       <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1149,12 +1220,12 @@
       <c r="D15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A16" s="17"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="4" t="s">
         <v>40</v>
       </c>
@@ -1167,7 +1238,7 @@
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A17" s="17"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="6" t="s">
         <v>42</v>
       </c>
@@ -1177,102 +1248,133 @@
       <c r="D17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="13"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="33" x14ac:dyDescent="0.15">
+      <c r="A19" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A20" s="19"/>
+      <c r="B20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A19" s="18"/>
-      <c r="B19" s="4" t="s">
+      <c r="C20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A20" s="18"/>
-      <c r="B20" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="5" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A21" s="10"/>
+      <c r="B21" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="13"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A22" s="10"/>
+      <c r="B22" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A23" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="B23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A21" s="19" t="s">
+      <c r="C23" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A24" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="B24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A22" s="18" t="s">
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="19"/>
+      <c r="B25" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="E25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="18"/>
-      <c r="B23" s="11" t="s">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B26" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B24" s="11" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B29" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="C29" s="21" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B30" s="21" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
   <mergeCells count="10">
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A23:A25"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="A1:E1"/>

--- a/slides/tt1/checking_points.xlsx
+++ b/slides/tt1/checking_points.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\suine\project\mindvault\slides\tt1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\suine\projects\mindvault\slides\tt1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{90CACBD7-0B83-4420-A457-3A83B8442119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD5C28C-99DC-4F54-84FF-DC9C3DD30C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务列表" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="WpsReserved_CellImgList" sheetId="2" state="veryHidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -51,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
   <si>
     <t>TODO：</t>
   </si>
@@ -71,9 +70,6 @@
     <t>结论</t>
   </si>
   <si>
-    <t>9654(Zen4)</t>
-  </si>
-  <si>
     <t>硬件配置</t>
   </si>
   <si>
@@ -87,9 +83,6 @@
   </si>
   <si>
     <t>NVME盘</t>
-  </si>
-  <si>
-    <t>？？ 有哪些 盘问题？</t>
   </si>
   <si>
     <t>BIOS配置</t>
@@ -348,9 +341,6 @@
     <t>否</t>
   </si>
   <si>
-    <t>不需要warmup，会跑3轮，取平均数</t>
-  </si>
-  <si>
     <t>OS</t>
   </si>
   <si>
@@ -408,90 +398,129 @@
     <t>384/384(2p)</t>
   </si>
   <si>
-    <t>512/512(2p)</t>
-  </si>
-  <si>
     <t>版本配置</t>
   </si>
   <si>
+    <t>测试脚本</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>./bin/cube-bench</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>待确认（当前使用的是 sandbox-code:latest)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙箱操作系统</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Host核数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>24*64G DDR5 6400MT/s</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>9654(Zen4)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>9755(Zen5)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TDP/PPT control = Manual
+TDP/PPT = 360</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMA nodes per socket = NPS4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙箱配置</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2C2GB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>待确认</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>31d911e430fdf8a8879bd062b8e78066c1a8e89d（v7.1.0）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>install.sh 指定</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>是 使用 -w 参数指定 warmup 3轮</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>测试版本</t>
-  </si>
-  <si>
-    <t>commit id （tag）</t>
-  </si>
-  <si>
-    <t>Cmmit ID</t>
-  </si>
-  <si>
-    <t>测试的 CubeSandbox repo 的 版本</t>
-  </si>
-  <si>
-    <t>docker / docker-compose 版本</t>
-  </si>
-  <si>
-    <t>（为何需要）</t>
-  </si>
-  <si>
-    <t>镜像版本</t>
-  </si>
-  <si>
-    <t>install.sh 是否指定了镜像版本</t>
-  </si>
-  <si>
-    <t>测试脚本</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>./bin/cube-bench</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>模板镜像</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>待确认（当前使用的是 sandbox-code:latest)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>沙箱操作系统</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Host核数</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>沙箱 vCore</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>沙箱内存</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>24*64G DDR5 6400MT/s</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>外围依赖镜像版本</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>待确认（9654支持的 内存速度）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>512/521(2p)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>docker</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>docker-compose</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>v5.1.4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>cube-sandbox-builder:ubuntu2004</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>build 镜像版本（rustc/go/clang/llvm/node/python 等）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取 OpenEuler Image 中 Docker 版本</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -520,14 +549,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -541,8 +562,15 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,8 +601,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -595,9 +629,18 @@
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -606,88 +649,145 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -994,396 +1094,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.5"/>
+    <col min="2" max="2" width="12.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.375" customWidth="1"/>
-    <col min="2" max="2" width="47.625" customWidth="1"/>
-    <col min="3" max="3" width="45.625" customWidth="1"/>
-    <col min="4" max="4" width="56.875" customWidth="1"/>
-    <col min="5" max="5" width="38.5" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="47.6640625" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" customWidth="1"/>
+    <col min="4" max="5" width="56.88671875" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="2">
+        <v>950</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="46.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" ht="46.8" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23"/>
+      <c r="B12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.15">
-      <c r="A3" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.15">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="2">
-        <v>950</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A5" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="25" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="21"/>
+    </row>
+    <row r="15" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="29"/>
+      <c r="B19" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="32"/>
+    </row>
+    <row r="20" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A6" s="18"/>
-      <c r="B6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A8" s="18"/>
-      <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="49.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="18"/>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A10" s="18"/>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A11" s="18"/>
-      <c r="B11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="49.5" x14ac:dyDescent="0.15">
-      <c r="A12" s="18"/>
-      <c r="B12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A13" s="18"/>
-      <c r="B13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A14" s="18"/>
-      <c r="B14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A15" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A16" s="18"/>
-      <c r="B16" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A17" s="18"/>
-      <c r="B17" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A18" s="24"/>
-      <c r="B18" s="23" t="s">
+      <c r="C21" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="41"/>
+    </row>
+    <row r="23" spans="1:6" ht="32.4" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="41"/>
+    </row>
+    <row r="24" spans="1:6" ht="16.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C24" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="41"/>
+    </row>
+    <row r="25" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="29"/>
+      <c r="B25" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="33" x14ac:dyDescent="0.15">
-      <c r="A19" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A20" s="19"/>
-      <c r="B20" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A21" s="10"/>
-      <c r="B21" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A22" s="10"/>
-      <c r="B22" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A23" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-    </row>
-    <row r="24" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A24" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="19"/>
-      <c r="B25" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B26" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B29" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B30" s="21" t="s">
-        <v>61</v>
-      </c>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="42"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <mergeCells count="10">
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C3:D3"/>
+  <mergeCells count="21">
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A17:A19"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1391,21 +1532,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="3"/>
-  <pixelatorList sheetStid="2"/>
-</pixelators>
+<autofilters xmlns="https://web.wps.cn/et/2018/main"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1427,11 +1564,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<autofilters xmlns="https://web.wps.cn/et/2018/main"/>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="3"/>
+  <pixelatorList sheetStid="2"/>
+</pixelators>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5662047-3127-477A-AC3A-1D340467FB41}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -1449,7 +1590,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5662047-3127-477A-AC3A-1D340467FB41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
